--- a/content/post/2025_11_09 BG MF-VAR/BGMFVAR_250911.xlsx
+++ b/content/post/2025_11_09 BG MF-VAR/BGMFVAR_250911.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bblagov\Dropbox\Website\2025web\content\post\2025_11_09 BG MF-VAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86308946-369F-4D93-9101-7B29FF1279CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BC5750-D3C9-4947-94F5-6D5F322A438D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{244FC629-5F10-4235-9D1A-45435594493E}"/>
   </bookViews>
@@ -3019,9 +3019,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>541940</xdr:colOff>
-      <xdr:row>261</xdr:row>
-      <xdr:rowOff>4598</xdr:rowOff>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>260</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
